--- a/fhir/StructureDefinition-questionnaire-response-reference.xlsx
+++ b/fhir/StructureDefinition-questionnaire-response-reference.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.17.1</t>
+    <t>2.18.0</t>
   </si>
   <si>
     <t>Name</t>

--- a/fhir/StructureDefinition-questionnaire-response-reference.xlsx
+++ b/fhir/StructureDefinition-questionnaire-response-reference.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.18.0</t>
+    <t>2.19.1</t>
   </si>
   <si>
     <t>Name</t>

--- a/fhir/StructureDefinition-questionnaire-response-reference.xlsx
+++ b/fhir/StructureDefinition-questionnaire-response-reference.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.19.1</t>
+    <t>2.19.2</t>
   </si>
   <si>
     <t>Name</t>

--- a/fhir/StructureDefinition-questionnaire-response-reference.xlsx
+++ b/fhir/StructureDefinition-questionnaire-response-reference.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.19.3</t>
+    <t>2.19.4</t>
   </si>
   <si>
     <t>Name</t>

--- a/fhir/StructureDefinition-questionnaire-response-reference.xlsx
+++ b/fhir/StructureDefinition-questionnaire-response-reference.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.19.4</t>
+    <t>2.21.0</t>
   </si>
   <si>
     <t>Name</t>

--- a/fhir/StructureDefinition-questionnaire-response-reference.xlsx
+++ b/fhir/StructureDefinition-questionnaire-response-reference.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.21.0</t>
+    <t>2.23.0</t>
   </si>
   <si>
     <t>Name</t>

--- a/fhir/StructureDefinition-questionnaire-response-reference.xlsx
+++ b/fhir/StructureDefinition-questionnaire-response-reference.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.23.0</t>
+    <t>2.23.1</t>
   </si>
   <si>
     <t>Name</t>

--- a/fhir/StructureDefinition-questionnaire-response-reference.xlsx
+++ b/fhir/StructureDefinition-questionnaire-response-reference.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.23.1</t>
+    <t>2.23.2</t>
   </si>
   <si>
     <t>Name</t>

--- a/fhir/StructureDefinition-questionnaire-response-reference.xlsx
+++ b/fhir/StructureDefinition-questionnaire-response-reference.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.23.2</t>
+    <t>2.23.5</t>
   </si>
   <si>
     <t>Name</t>

--- a/fhir/StructureDefinition-questionnaire-response-reference.xlsx
+++ b/fhir/StructureDefinition-questionnaire-response-reference.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.23.5</t>
+    <t>2.24.0</t>
   </si>
   <si>
     <t>Name</t>

--- a/fhir/StructureDefinition-questionnaire-response-reference.xlsx
+++ b/fhir/StructureDefinition-questionnaire-response-reference.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.24.0</t>
+    <t>2.19.5</t>
   </si>
   <si>
     <t>Name</t>

--- a/fhir/StructureDefinition-questionnaire-response-reference.xlsx
+++ b/fhir/StructureDefinition-questionnaire-response-reference.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.19.5</t>
+    <t>2.25.0</t>
   </si>
   <si>
     <t>Name</t>

--- a/fhir/StructureDefinition-questionnaire-response-reference.xlsx
+++ b/fhir/StructureDefinition-questionnaire-response-reference.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.25.0</t>
+    <t>1.25.1</t>
   </si>
   <si>
     <t>Name</t>

--- a/fhir/StructureDefinition-questionnaire-response-reference.xlsx
+++ b/fhir/StructureDefinition-questionnaire-response-reference.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.25.1</t>
+    <t>2.26.0</t>
   </si>
   <si>
     <t>Name</t>
